--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -413,38 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Distance 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
@@ -456,23 +446,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Fiducial 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83655</v>
+        <v>124.20061</v>
       </c>
       <c r="D2" t="n">
-        <v>16.74523</v>
+        <v>87.41251</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77958</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.05138</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.82441</v>
+        <v>90.44069</v>
+      </c>
+      <c r="F2" t="n">
+        <v>522.7017499999999</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +469,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88059</v>
+        <v>125.91222</v>
       </c>
       <c r="D3" t="n">
-        <v>16.86661</v>
+        <v>87.47033</v>
       </c>
       <c r="E3" t="n">
-        <v>16.73746</v>
+        <v>89.68624</v>
       </c>
       <c r="F3" t="n">
-        <v>43.12397</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.79869</v>
+        <v>519.58531</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +487,17 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>121.79445</v>
       </c>
       <c r="D4" t="n">
-        <v>17.04601</v>
+        <v>86.28691000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>16.9589</v>
+        <v>93.65494</v>
       </c>
       <c r="F4" t="n">
-        <v>43.40208</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05062</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.82839</v>
+        <v>513.97899</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +506,17 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>120.85457</v>
       </c>
       <c r="D5" t="n">
-        <v>16.74914</v>
+        <v>85.6369</v>
       </c>
       <c r="E5" t="n">
-        <v>16.47404</v>
+        <v>94.02124000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>42.36919</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.05157</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.84656</v>
+        <v>518.87715</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +526,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.82711</v>
+        <v>125.14746</v>
       </c>
       <c r="D6" t="n">
-        <v>16.88758</v>
+        <v>86.40085999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68659</v>
+        <v>90.45757</v>
       </c>
       <c r="F6" t="n">
-        <v>43.2384</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05004</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>510.52973</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +545,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.97469</v>
+        <v>121.53167</v>
       </c>
       <c r="D7" t="n">
-        <v>16.71283</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>86.75451</v>
+      </c>
+      <c r="E7" t="n">
+        <v>93.23715</v>
       </c>
       <c r="F7" t="n">
-        <v>43.12853</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.0503</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.85701</v>
+        <v>529.63603</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +564,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.69237</v>
+        <v>122.1332</v>
       </c>
       <c r="D8" t="n">
-        <v>16.76706</v>
+        <v>86.7701</v>
       </c>
       <c r="E8" t="n">
-        <v>17.02346</v>
+        <v>91.26804</v>
       </c>
       <c r="F8" t="n">
-        <v>42.47407</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.05087</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.84809</v>
+        <v>521.15793</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +583,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.04079</v>
+        <v>119.94065</v>
       </c>
       <c r="D9" t="n">
-        <v>16.61913</v>
+        <v>88.16658</v>
       </c>
       <c r="E9" t="n">
-        <v>16.92064</v>
+        <v>91.76085</v>
       </c>
       <c r="F9" t="n">
-        <v>43.16771</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.05074</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.83914</v>
+        <v>529.35187</v>
       </c>
     </row>
     <row r="10">
@@ -663,33 +602,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.20434</v>
+        <v>118.78101</v>
       </c>
       <c r="D10" t="n">
-        <v>16.90762</v>
+        <v>87.99632</v>
       </c>
       <c r="E10" t="n">
-        <v>17.09473</v>
+        <v>92.24096</v>
       </c>
       <c r="F10" t="n">
-        <v>42.91069</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05066</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.86332</v>
+        <v>528.95153</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Diameter</t>
         </is>
       </c>
     </row>
@@ -701,14 +634,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Micro Bump 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>8.57128</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13505</v>
+        <v>24.10872</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +651,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>8.7582</v>
       </c>
       <c r="D13" t="n">
-        <v>1.15772</v>
+        <v>24.69424</v>
       </c>
     </row>
     <row r="14">
@@ -731,10 +664,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>8.873250000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>1.12354</v>
+        <v>24.64047</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +677,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>8.743919999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.12607</v>
+        <v>24.23112</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +690,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8.511430000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13504</v>
+        <v>24.63997</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +703,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.626709999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1255</v>
+        <v>24.35257</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +716,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.71771</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11486</v>
+        <v>24.71051</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +729,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>8.681340000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1.13026</v>
+        <v>24.43144</v>
       </c>
     </row>
     <row r="20">
@@ -809,51 +742,41 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>8.92873</v>
       </c>
       <c r="D20" t="n">
-        <v>1.15461</v>
+        <v>24.69504</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -865,32 +788,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7434500000000001</v>
+        <v>16.99002</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08222</v>
+        <v>16.77789</v>
       </c>
       <c r="E22" t="n">
-        <v>0.62652</v>
+        <v>16.9425</v>
       </c>
       <c r="F22" t="n">
-        <v>0.98492</v>
+        <v>42.42446</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11017</v>
+        <v>0.05109</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09351</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12803</v>
+        <v>1.84317</v>
       </c>
     </row>
     <row r="23">
@@ -900,28 +817,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.74714</v>
+        <v>16.9511</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08136</v>
+        <v>16.59517</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60736</v>
+        <v>16.76631</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9922800000000001</v>
+        <v>42.90634</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10945</v>
+        <v>0.05046</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09383</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12894</v>
+        <v>1.83239</v>
       </c>
     </row>
     <row r="24">
@@ -931,28 +842,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75229</v>
+        <v>17.11071</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08227</v>
+        <v>16.67791</v>
       </c>
       <c r="E24" t="n">
-        <v>0.61061</v>
+        <v>16.88779</v>
       </c>
       <c r="F24" t="n">
-        <v>0.97605</v>
+        <v>42.71216</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1114</v>
+        <v>0.05127</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09361999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12752</v>
+        <v>1.82678</v>
       </c>
     </row>
     <row r="25">
@@ -962,28 +867,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.77054</v>
+        <v>17.25286</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08026</v>
+        <v>16.58014</v>
       </c>
       <c r="E25" t="n">
-        <v>0.63144</v>
+        <v>17.07509</v>
       </c>
       <c r="F25" t="n">
-        <v>0.93989</v>
+        <v>43.41261</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10932</v>
+        <v>0.05146</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.0955</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12984</v>
+        <v>1.86891</v>
       </c>
     </row>
     <row r="26">
@@ -993,28 +892,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75901</v>
+        <v>17.15894</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08082</v>
+        <v>16.69526</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60582</v>
+        <v>17.06333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97102</v>
+        <v>42.10893</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11012</v>
+        <v>0.05061</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09417</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1275</v>
+        <v>1.87855</v>
       </c>
     </row>
     <row r="27">
@@ -1024,28 +917,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7501100000000001</v>
+        <v>17.12437</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0824</v>
+        <v>16.30641</v>
       </c>
       <c r="E27" t="n">
-        <v>0.62</v>
+        <v>17.11184</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9824000000000001</v>
+        <v>43.55101</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10913</v>
+        <v>0.05142</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09561</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12658</v>
+        <v>1.8609</v>
       </c>
     </row>
     <row r="28">
@@ -1055,28 +942,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75419</v>
+        <v>17.08055</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08187</v>
+        <v>16.87535</v>
       </c>
       <c r="E28" t="n">
-        <v>0.62851</v>
+        <v>17.01475</v>
       </c>
       <c r="F28" t="n">
-        <v>0.98024</v>
+        <v>43.23153</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11152</v>
+        <v>0.05248</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13024</v>
+        <v>1.83579</v>
       </c>
     </row>
     <row r="29">
@@ -1086,28 +967,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7476</v>
+        <v>16.90591</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08269</v>
+        <v>16.68012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.61028</v>
+        <v>16.86098</v>
       </c>
       <c r="F29" t="n">
-        <v>0.98985</v>
+        <v>42.93318</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11203</v>
+        <v>0.04988</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00778</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09322999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12663</v>
+        <v>1.84209</v>
       </c>
     </row>
     <row r="30">
@@ -1117,28 +992,348 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.76691</v>
+        <v>17.00488</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08209</v>
+        <v>16.74213</v>
       </c>
       <c r="E30" t="n">
-        <v>0.61409</v>
+        <v>16.76202</v>
       </c>
       <c r="F30" t="n">
-        <v>0.99566</v>
+        <v>42.23583</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11212</v>
+        <v>0.05112</v>
       </c>
       <c r="H30" t="n">
+        <v>1.82953</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.74397</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08117000000000001</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.59831</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.99155</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10852</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09202</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1277</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7452</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08222</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.60997</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.95486</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11081</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09422999999999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12817</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.75109</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08279</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.62541</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.98466</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11294</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09402000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12725</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7505500000000001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0835</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.61715</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.98089</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10929</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09429</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12557</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7793099999999999</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.60849</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9561500000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10934</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09476999999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12934</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.75828</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.61653</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.99427</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.10825</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09408999999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12942</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.77188</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08216</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.62486</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9702</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.10865</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09452000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12815</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.75827</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08105999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.61426</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.98439</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10911</v>
+      </c>
+      <c r="H39" t="n">
         <v>0.00764</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09465</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12718</v>
+      <c r="I39" t="n">
+        <v>0.09422999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12895</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.76518</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08122</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.61329</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.96871</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10852</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09263</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12945</v>
       </c>
     </row>
   </sheetData>
